--- a/LISTAS_ORDENADAS/MI/Fratachos Cinta de perciana Articulos de madera/FRATACHO PINO.xlsx
+++ b/LISTAS_ORDENADAS/MI/Fratachos Cinta de perciana Articulos de madera/FRATACHO PINO.xlsx
@@ -745,14 +745,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="29" t="n">
-        <v>45209.57783584008</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="24">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -798,26 +794,6 @@
       </c>
       <c r="E11" s="9" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="24">
       <c r="A32" s="13" t="inlineStr">
         <is>
@@ -920,10 +896,8 @@
         </is>
       </c>
       <c r="C37" s="21" t="n"/>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D37" s="15" t="n">
+        <v>195.902</v>
       </c>
       <c r="E37" s="3" t="n"/>
       <c r="F37" s="16" t="n"/>
@@ -940,10 +914,8 @@
         </is>
       </c>
       <c r="C38" s="21" t="n"/>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D38" s="17" t="n">
+        <v>220.756</v>
       </c>
       <c r="E38" s="3" t="n"/>
       <c r="F38" s="16" t="n"/>
@@ -960,10 +932,8 @@
         </is>
       </c>
       <c r="C39" s="21" t="n"/>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D39" s="17" t="n">
+        <v>266.077</v>
       </c>
       <c r="F39" s="16" t="n"/>
     </row>
@@ -979,14 +949,11 @@
         </is>
       </c>
       <c r="C40" s="21" t="n"/>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="17" t="n">
+        <v>346.484</v>
       </c>
       <c r="F40" s="16" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="24">
       <c r="A42" s="12" t="inlineStr">
         <is>
@@ -994,16 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="24">
       <c r="A53" s="4" t="n"/>
     </row>
@@ -1012,19 +969,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
